--- a/FundingRadar.xlsx
+++ b/FundingRadar.xlsx
@@ -5,18 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rachel.roday\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rachel.roday\Documents\Funding Radar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF469984-6E6D-41FD-9363-D9436AD1B6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92696A9A-5A81-4B1A-864C-B4C9369DE5C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="6770" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{BC9A3F9B-EEE3-4E84-BDD8-7C6D0C4B24D8}"/>
+    <workbookView xWindow="-38510" yWindow="6770" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="4" xr2:uid="{BC9A3F9B-EEE3-4E84-BDD8-7C6D0C4B24D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Source" sheetId="1" r:id="rId1"/>
     <sheet name="Scraper Fields" sheetId="2" r:id="rId2"/>
     <sheet name="Scraper Keywords" sheetId="3" r:id="rId3"/>
     <sheet name="Rachel Keywords" sheetId="4" r:id="rId4"/>
+    <sheet name="Actual Opportunites - Apply!" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="303">
   <si>
     <t>Category</t>
   </si>
@@ -762,13 +763,202 @@
   </si>
   <si>
     <t>Keywords</t>
+  </si>
+  <si>
+    <t>Kushlan Research Award</t>
+  </si>
+  <si>
+    <t>Nisbet Research Award</t>
+  </si>
+  <si>
+    <t>Waterbird Society Research Grant</t>
+  </si>
+  <si>
+    <t>Proposal</t>
+  </si>
+  <si>
+    <t>Due Date</t>
+  </si>
+  <si>
+    <t>Money Amount</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>Fieldwork / Research Grant</t>
+  </si>
+  <si>
+    <t>01 February</t>
+  </si>
+  <si>
+    <t>Up to $7,000 USD</t>
+  </si>
+  <si>
+    <t>https://waterbirds.org/research-grants/kushlan-research-award/</t>
+  </si>
+  <si>
+    <t>Up to $5,000 USD</t>
+  </si>
+  <si>
+    <t>https://waterbirds.org/research-grants/nisbet-research-award/</t>
+  </si>
+  <si>
+    <t>https://waterbirds.org/research-grants/waterbird-society-research-grant/</t>
+  </si>
+  <si>
+    <t>IASC / APECS / Prince Albert II Foundation</t>
+  </si>
+  <si>
+    <t>IASC Fellowship Program 2026</t>
+  </si>
+  <si>
+    <t>Fellowship / Professional Development</t>
+  </si>
+  <si>
+    <t>TBD (annual call)</t>
+  </si>
+  <si>
+    <t>Variable (participation and engagement support)</t>
+  </si>
+  <si>
+    <t>https://www.apecs.is</t>
+  </si>
+  <si>
+    <t>Fellowship supporting early-career participation in IASC activities and Arctic research networks</t>
+  </si>
+  <si>
+    <t>International Arctic Science Committee (IASC)</t>
+  </si>
+  <si>
+    <t>Arctic Science Summit Week Funding</t>
+  </si>
+  <si>
+    <t>Conference Travel</t>
+  </si>
+  <si>
+    <t>Varies by year</t>
+  </si>
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>Travel support opportunities associated with Arctic Science Summit Week (ASSW)</t>
+  </si>
+  <si>
+    <t>University of Oslo</t>
+  </si>
+  <si>
+    <t>Gender Equality Funding Guidelines</t>
+  </si>
+  <si>
+    <t>Institutional Funding Resource</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>https://www.mn.uio.no/english/about/gender-equality/2017-guidelines-eng.pdf</t>
+  </si>
+  <si>
+    <t>Resource describing funding mechanisms and support related to gender equality initiatives</t>
+  </si>
+  <si>
+    <t>HK-dir (Norwegian Directorate for Higher Education and Skills)</t>
+  </si>
+  <si>
+    <t>Arctic Research and Studies Call for Proposals 2025</t>
+  </si>
+  <si>
+    <t>Research Grant / Mobility Grant</t>
+  </si>
+  <si>
+    <t>Annual call</t>
+  </si>
+  <si>
+    <t>Varies by call</t>
+  </si>
+  <si>
+    <t>https://hkdir.no/en/grants-and-open-calls/arctic-research-and-studies-call-for-proposals-2025</t>
+  </si>
+  <si>
+    <t>Supports Arctic research, education, collaboration, and mobility activities</t>
+  </si>
+  <si>
+    <t>Pacific Seabird Group (PSG)</t>
+  </si>
+  <si>
+    <t>Student Research Grant (SRG)</t>
+  </si>
+  <si>
+    <t>Fieldwork Grant / Research Grant</t>
+  </si>
+  <si>
+    <t>06 February 2026</t>
+  </si>
+  <si>
+    <t>3 to 5 grants of $3,000 USD each</t>
+  </si>
+  <si>
+    <t>https://pacificseabirdgroup.org/student-research-grant/</t>
+  </si>
+  <si>
+    <t>Open worldwide to BA, BS, MS, MA, and PhD students conducting seabird research. Funds may be used for fieldwork, travel to field sites, equipment, permits, laboratory supplies, and dissemination of results. Cannot be used for salary, stipend, tuition, or overhead. Awardees present at PSG Annual Meeting the following year.</t>
+  </si>
+  <si>
+    <t>Student Research Grants</t>
+  </si>
+  <si>
+    <t>TBD (2027 cycle)</t>
+  </si>
+  <si>
+    <t>Up to $4,000 USD</t>
+  </si>
+  <si>
+    <t>https://americanornithology.org/awards-grants/research-grants/student-research-grants/</t>
+  </si>
+  <si>
+    <t>Supports undergraduate, graduate student, and postdoctoral research in avian biology. Includes multiple named grants. AOS membership required. Geographic eligibility for projects outside North America unclear; contacted committee for clarification. Also contacted committee regarding 2027 application opening date.</t>
+  </si>
+  <si>
+    <t>British Ecological Society</t>
+  </si>
+  <si>
+    <t>Training and Travel Grants</t>
+  </si>
+  <si>
+    <t>Conference Travel / Training</t>
+  </si>
+  <si>
+    <t>Multiple rounds annually</t>
+  </si>
+  <si>
+    <t>https://www.britishecologicalsociety.org/content/training-and-travel-grants/</t>
+  </si>
+  <si>
+    <t>Supports PhD students and postgraduate researchers attending training courses, workshops, and conferences. Membership required. Appears open internationally.</t>
+  </si>
+  <si>
+    <t>Small Research Grants</t>
+  </si>
+  <si>
+    <t>March and September rounds</t>
+  </si>
+  <si>
+    <t>Up to £5,000</t>
+  </si>
+  <si>
+    <t>https://www.britishecologicalsociety.org/content/small-research-grants/</t>
+  </si>
+  <si>
+    <t>Supports innovative ecological research where alternative funding is limited. Membership required. Appears open internationally.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -790,16 +980,35 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F5F5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -807,17 +1016,38 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFE6E6E6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFE6E6E6"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFE6E6E6"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFE6E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2721,4 +2951,287 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2833E873-9E36-40C7-AE8D-9EBD01EA708F}">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="3" width="37.88671875" customWidth="1"/>
+    <col min="4" max="4" width="32.21875" customWidth="1"/>
+    <col min="5" max="5" width="21.88671875" customWidth="1"/>
+    <col min="6" max="6" width="33" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="38.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="38.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="38.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="32.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="32.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="32.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="32.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="37.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="37.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>302</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>